--- a/resultados/saomateusdosul/erros_varredura.xlsx
+++ b/resultados/saomateusdosul/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,6 +1820,622 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qBxTxw-/</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:57:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/obras/</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>404</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:16:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/obras/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:16:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/educacao-e-cultura/</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>404</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:16:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/educacao-e-cultura/</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1049/iii-polskie-smaki/</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:17:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/diario-oficial/dsozzo/</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:30:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1073/inscricoes-para-o-conselho-municipal-de-saude---comsas-profissionais-da-saude/</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:49:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1072/inscricoes-para-o-conselho-municipal-de-saude---comsas-entidades/</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1076/inscricao-feira-depascoa/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1060/recurso-pss-saude/</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:54:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1047/processo-seletivo-simplificado/</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/servicos/1119/2-desafio-de-ideias--inova-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/dispensa-de-licitacao-n--011-2020---aquisicao-emergencial-oximetro e-kit-laringoscopio/</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>404</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/dispensa-de-licitacao-n--011-2020---aquisicao-emergencial-oximetro e-kit-laringoscopio/</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:56:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/transito/</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>404</v>
+      </c>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/transito/</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:29:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/administracao/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>404</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:29:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/administracao/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:29:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/industria-e-comercio/</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>404</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:29:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/industria-e-comercio/</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nGxLo-x/</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:36:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saomateusdosul/erros_varredura.xlsx
+++ b/resultados/saomateusdosul/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2227"/>
+  <dimension ref="A1:F2244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62776,6 +62776,482 @@
         </is>
       </c>
     </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/GBoLjL/</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2228" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:45:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/sqoPLj/</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2229" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/sdojzT/</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2230" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:07:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/ndojLw/</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2231" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/qRojAT/</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D2232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2232" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:54:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/qnoozA/</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2233" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2233" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:57:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/destaque/situacao-da-six-chega-a-dilma-e-ministro-garante-a-ledur-que-unidade-sera-mantida/</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D2234" t="n">
+        <v>404</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2234" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:37:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/destaque/situacao-da-six-chega-a-dilma-e-ministro-garante-a-ledur-que-unidade-sera-mantida/</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2235" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:37:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/fale-com-o-prefeito/</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D2236" t="n">
+        <v>404</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2236" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:37:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/nqjATz/</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D2237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2237" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/licitacoes/hGjA-o/</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D2238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2238" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/servicos/agencia-do-trabalhador/</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D2239" t="n">
+        <v>404</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2239" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:19:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/educacao</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D2240" t="n">
+        <v>404</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2240" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/educacao/</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D2241" t="n">
+        <v>404</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2241" t="inlineStr">
+        <is>
+          <t>2026-08-11 23:23:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>http://www.saomateusdosul.pr.gov.br/categorias/educacao/</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D2242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2242" t="inlineStr">
+        <is>
+          <t>2026-08-11 23:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nCxjLwz/</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D2243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2243" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:21:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/KCxjxTP/</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D2244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2244" t="inlineStr">
+        <is>
+          <t>2026-08-12 07:49:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saomateusdosul/erros_varredura.xlsx
+++ b/resultados/saomateusdosul/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2244"/>
+  <dimension ref="A1:F2314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63252,6 +63252,1966 @@
         </is>
       </c>
     </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hRxoAjA/</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2245" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/GhxoAPT/</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2246" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/sRxoAPT/</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2247" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/sGxoAPL/</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2248" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/KqxoAPP/</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2249" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nsxoAPP/</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2250" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/dqxoAPj/</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2251" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/GBxoAPj/</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2252" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/sdxoAPo/</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2253" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/GnxoAPx/</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2254" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/RKxoAPx/</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2255" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/KsxoAPz/</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2256" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2256" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/RsxoAPz/</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2257" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2257" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nnxoALA/</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2258" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:07:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/KR-joow/</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2259" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Cs-jo-o/</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2260" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2260" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Gn-jo-o/</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2261" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/sC-jo--/</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2262" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2262" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qK-jo-A/</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2263" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2263" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:34:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hR-joxw/</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2264" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:34:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nh-joxL/</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2265" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:36:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Kd-joxP/</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2266" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/KC-joxP/</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2267" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Gn-joxj/</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2268" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qG-joAw/</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2269" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2269" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:41:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hs-joAz/</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2270" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:41:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CdxT-jP/</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D2271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2271" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2271" t="inlineStr">
+        <is>
+          <t>2026-08-20 14:33:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Rsxwzjz/</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2272" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2272" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nqxwzjT/</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2273" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hKxwzjT/</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2274" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nRxwzjL/</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2275" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hBxwzjL/</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2276" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CKxwzjP/</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2277" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hdxwzjP/</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2278" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Csxwzjj/</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2279" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qsxwzjo/</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2280" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nBxwzjo/</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2281" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/ChxTTTL/</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2282" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2282" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qGxwzjA/</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2283" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qRxwzow/</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2284" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/KGxwzoj/</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2285" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:26:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Knxwzoj/</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2286" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qBxTTTx/</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2287" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:32:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qhxTPPT/</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2288" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hdxTPPT/</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2289" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/RCxwjoL/</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2290" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2290" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/GhxwjoL/</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2291" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/GqxwjoP/</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2292" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2292" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qsxwjoP/</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2293" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CRxTPPL/</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2294" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CBxTPPL/</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2295" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Chxwjoj/</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2296" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/dRxwjoj/</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2297" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/sdxwjoo/</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2298" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/dRxTPPP/</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2299" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/dCxTPPj/</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2300" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CsxTPPj/</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2301" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nGxwjox/</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2302" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Rnxwjox/</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2303" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CCxTPPo/</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2304" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/dqxTPPo/</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2305" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/CCxwjoA/</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2306" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/RdxTPP-/</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2307" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/RBxTPP-/</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2308" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Cqxwj-w/</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2309" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/qKxwj-w/</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2310" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/nCxTPPx/</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2311" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2311" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/hGxwj-z/</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2312" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:43:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/RKxwj-T/</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2313" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:44:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/download/legislacao/Kqxwj-L/</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2314" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2314" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:44:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
